--- a/docs/assets/coremeta4cat_vocabulary.xlsx
+++ b/docs/assets/coremeta4cat_vocabulary.xlsx
@@ -1412,7 +1412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J285"/>
+  <dimension ref="A1:J293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -13147,6 +13147,324 @@
         </is>
       </c>
       <c r="J285" s="13" t="inlineStr">
+        <is>
+          <t>Gas flow rate maintained during calcination.</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="16" t="inlineStr">
+        <is>
+          <t>YueTestSynthesis</t>
+        </is>
+      </c>
+      <c r="B286" s="16" t="inlineStr">
+        <is>
+          <t>class</t>
+        </is>
+      </c>
+      <c r="C286" s="16" t="inlineStr">
+        <is>
+          <t>PreparationMethod</t>
+        </is>
+      </c>
+      <c r="D286" s="16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E286" s="16" t="inlineStr"/>
+      <c r="F286" s="16" t="inlineStr"/>
+      <c r="G286" s="16" t="inlineStr"/>
+      <c r="H286" s="16" t="inlineStr"/>
+      <c r="I286" s="16" t="inlineStr">
+        <is>
+          <t>coremeta4cat:YueTestSynthesis</t>
+        </is>
+      </c>
+      <c r="J286" s="16" t="inlineStr">
+        <is>
+          <t>Catalyst preparation by exsolution: testing Yue changes in Synthesis
+a perovskite oxide surface by reduction/oxidation cycling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="15" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B287" s="15" t="inlineStr">
+        <is>
+          <t>slot</t>
+        </is>
+      </c>
+      <c r="C287" s="15" t="inlineStr">
+        <is>
+          <t>YueTestSynthesis</t>
+        </is>
+      </c>
+      <c r="D287" s="15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E287" s="15" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F287" s="15" t="inlineStr"/>
+      <c r="G287" s="15" t="inlineStr"/>
+      <c r="H287" s="15" t="inlineStr"/>
+      <c r="I287" s="15" t="inlineStr"/>
+      <c r="J287" s="15" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="13" t="inlineStr">
+        <is>
+          <t>has calcination temperature range</t>
+        </is>
+      </c>
+      <c r="B288" s="13" t="inlineStr">
+        <is>
+          <t>slot</t>
+        </is>
+      </c>
+      <c r="C288" s="13" t="inlineStr">
+        <is>
+          <t>YueTestSynthesis</t>
+        </is>
+      </c>
+      <c r="D288" s="13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E288" s="13" t="inlineStr">
+        <is>
+          <t>QuantitativeRange</t>
+        </is>
+      </c>
+      <c r="F288" s="13" t="inlineStr"/>
+      <c r="G288" s="13" t="inlineStr"/>
+      <c r="H288" s="13" t="inlineStr"/>
+      <c r="I288" s="13" t="inlineStr">
+        <is>
+          <t>coremeta4cat:hasCalcinationTemperatureRange</t>
+        </is>
+      </c>
+      <c r="J288" s="13" t="inlineStr">
+        <is>
+          <t>Temperature range of the calcination programme (initial -&gt; final temperature),
+provided as a QuantitativeRange. Unit: Degree Celsius.</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="13" t="inlineStr">
+        <is>
+          <t>has calcination dwelling time</t>
+        </is>
+      </c>
+      <c r="B289" s="13" t="inlineStr">
+        <is>
+          <t>slot</t>
+        </is>
+      </c>
+      <c r="C289" s="13" t="inlineStr">
+        <is>
+          <t>YueTestSynthesis</t>
+        </is>
+      </c>
+      <c r="D289" s="13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E289" s="13" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="F289" s="13" t="inlineStr"/>
+      <c r="G289" s="13" t="inlineStr"/>
+      <c r="H289" s="13" t="inlineStr"/>
+      <c r="I289" s="13" t="inlineStr">
+        <is>
+          <t>VOC4CAT:0000060</t>
+        </is>
+      </c>
+      <c r="J289" s="13" t="inlineStr">
+        <is>
+          <t>Time held at the final calcination temperature.</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="13" t="inlineStr">
+        <is>
+          <t>number of cycles</t>
+        </is>
+      </c>
+      <c r="B290" s="13" t="inlineStr">
+        <is>
+          <t>slot</t>
+        </is>
+      </c>
+      <c r="C290" s="13" t="inlineStr">
+        <is>
+          <t>YueTestSynthesis</t>
+        </is>
+      </c>
+      <c r="D290" s="13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E290" s="13" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="F290" s="13" t="inlineStr"/>
+      <c r="G290" s="13" t="inlineStr"/>
+      <c r="H290" s="13" t="inlineStr"/>
+      <c r="I290" s="13" t="inlineStr">
+        <is>
+          <t>VOC4CAT:0008123</t>
+        </is>
+      </c>
+      <c r="J290" s="13" t="inlineStr">
+        <is>
+          <t>Number of repeated cycles in a process (e.g. ALD cycles, impregnation cycles).</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="13" t="inlineStr">
+        <is>
+          <t>has calcination atmosphere</t>
+        </is>
+      </c>
+      <c r="B291" s="13" t="inlineStr">
+        <is>
+          <t>slot</t>
+        </is>
+      </c>
+      <c r="C291" s="13" t="inlineStr">
+        <is>
+          <t>YueTestSynthesis</t>
+        </is>
+      </c>
+      <c r="D291" s="13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E291" s="13" t="inlineStr">
+        <is>
+          <t>CalcinationGaseousEnvironment</t>
+        </is>
+      </c>
+      <c r="F291" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G291" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H291" s="13" t="inlineStr"/>
+      <c r="I291" s="13" t="inlineStr">
+        <is>
+          <t>SIO:000008</t>
+        </is>
+      </c>
+      <c r="J291" s="13" t="inlineStr">
+        <is>
+          <t>Gaseous environment maintained during the calcination step.</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="13" t="inlineStr">
+        <is>
+          <t>has calcination heating rate</t>
+        </is>
+      </c>
+      <c r="B292" s="13" t="inlineStr">
+        <is>
+          <t>slot</t>
+        </is>
+      </c>
+      <c r="C292" s="13" t="inlineStr">
+        <is>
+          <t>YueTestSynthesis</t>
+        </is>
+      </c>
+      <c r="D292" s="13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E292" s="13" t="inlineStr">
+        <is>
+          <t>HeatingRate</t>
+        </is>
+      </c>
+      <c r="F292" s="13" t="inlineStr"/>
+      <c r="G292" s="13" t="inlineStr"/>
+      <c r="H292" s="13" t="inlineStr"/>
+      <c r="I292" s="13" t="inlineStr">
+        <is>
+          <t>VOC4CAT:0008116</t>
+        </is>
+      </c>
+      <c r="J292" s="13" t="inlineStr">
+        <is>
+          <t>Temperature ramp rate during the calcination step.</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="13" t="inlineStr">
+        <is>
+          <t>has calcination gas flow rate</t>
+        </is>
+      </c>
+      <c r="B293" s="13" t="inlineStr">
+        <is>
+          <t>slot</t>
+        </is>
+      </c>
+      <c r="C293" s="13" t="inlineStr">
+        <is>
+          <t>YueTestSynthesis</t>
+        </is>
+      </c>
+      <c r="D293" s="13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E293" s="13" t="inlineStr">
+        <is>
+          <t>VolumeFlowRate</t>
+        </is>
+      </c>
+      <c r="F293" s="13" t="inlineStr"/>
+      <c r="G293" s="13" t="inlineStr"/>
+      <c r="H293" s="13" t="inlineStr"/>
+      <c r="I293" s="13" t="inlineStr">
+        <is>
+          <t>VOC4CAT:0000056</t>
+        </is>
+      </c>
+      <c r="J293" s="13" t="inlineStr">
         <is>
           <t>Gas flow rate maintained during calcination.</t>
         </is>
